--- a/data/dividends_info_20260306.xlsx
+++ b/data/dividends_info_20260306.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>21.88999938964844</v>
+        <v>21.54999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>3.883051730014924</v>
+        <v>3.944315684885106</v>
       </c>
       <c r="J2" t="n">
         <v>108</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6.464000225067139</v>
+        <v>6.486000061035156</v>
       </c>
       <c r="I3" t="n">
-        <v>2.804764753827293</v>
+        <v>2.795251284210823</v>
       </c>
       <c r="J3" t="n">
         <v>108</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>33.61999893188477</v>
+        <v>32.97999954223633</v>
       </c>
       <c r="I5" t="n">
-        <v>5.948840165200679</v>
+        <v>6.064281466828616</v>
       </c>
       <c r="J5" t="n">
         <v>73</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.070000171661377</v>
+        <v>4.047999858856201</v>
       </c>
       <c r="I6" t="n">
-        <v>2.457002353372873</v>
+        <v>2.470355817360525</v>
       </c>
       <c r="J6" t="n">
         <v>73</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>75.40000152587891</v>
+        <v>75.04000091552734</v>
       </c>
       <c r="I7" t="n">
-        <v>1.379310316914317</v>
+        <v>1.385927488421448</v>
       </c>
       <c r="J7" t="n">
         <v>73</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>51.90000152587891</v>
+        <v>51.25</v>
       </c>
       <c r="I8" t="n">
-        <v>4.238920877300965</v>
+        <v>4.292682926829269</v>
       </c>
       <c r="J8" t="n">
         <v>73</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>19.14500045776367</v>
+        <v>19.1200008392334</v>
       </c>
       <c r="I9" t="n">
-        <v>4.126403662109287</v>
+        <v>4.131798981823028</v>
       </c>
       <c r="J9" t="n">
         <v>73</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.315000057220459</v>
+        <v>5.203999996185303</v>
       </c>
       <c r="I10" t="n">
-        <v>3.574788296415611</v>
+        <v>3.651037666012222</v>
       </c>
       <c r="J10" t="n">
         <v>73</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.56999969482422</v>
+        <v>10.42000007629395</v>
       </c>
       <c r="I11" t="n">
-        <v>4.087038907026044</v>
+        <v>4.145873290181859</v>
       </c>
       <c r="J11" t="n">
         <v>73</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24.63999938964844</v>
+        <v>24.92000007629395</v>
       </c>
       <c r="I12" t="n">
-        <v>1.785714329947789</v>
+        <v>1.765650074851187</v>
       </c>
       <c r="J12" t="n">
         <v>73</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="I13" t="n">
-        <v>2.568807339449541</v>
+        <v>2.545454545454545</v>
       </c>
       <c r="J13" t="n">
         <v>73</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2.822000026702881</v>
+        <v>2.785000085830688</v>
       </c>
       <c r="I14" t="n">
-        <v>10.63075822683492</v>
+        <v>10.77199248669029</v>
       </c>
       <c r="J14" t="n">
         <v>73</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22.68000030517578</v>
+        <v>22.61000061035156</v>
       </c>
       <c r="I15" t="n">
-        <v>2.645502609905497</v>
+        <v>2.653692984534026</v>
       </c>
       <c r="J15" t="n">
         <v>73</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.600000381469727</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="I16" t="n">
-        <v>5.93604624832303</v>
+        <v>6.027154473503674</v>
       </c>
       <c r="J16" t="n">
         <v>59</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18.89999961853027</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I17" t="n">
-        <v>3.968254048347555</v>
+        <v>3.989361864023487</v>
       </c>
       <c r="J17" t="n">
         <v>59</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.940000057220459</v>
+        <v>3.934999942779541</v>
       </c>
       <c r="I18" t="n">
-        <v>3.807106543694319</v>
+        <v>3.811944146917711</v>
       </c>
       <c r="J18" t="n">
         <v>59</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>12.30000019073486</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>1.60299997514244</v>
+        <v>1.643075</v>
       </c>
       <c r="J19" t="n">
         <v>59</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.210000038146973</v>
+        <v>2.214999914169312</v>
       </c>
       <c r="I20" t="n">
-        <v>2.941176419820373</v>
+        <v>2.93453735976224</v>
       </c>
       <c r="J20" t="n">
         <v>52</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.75</v>
+        <v>6.71999979019165</v>
       </c>
       <c r="I21" t="n">
-        <v>7.407407407407407</v>
+        <v>7.440476422778882</v>
       </c>
       <c r="J21" t="n">
         <v>45</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.68000030517578</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="I22" t="n">
-        <v>4.623287550435327</v>
+        <v>4.712041869131752</v>
       </c>
       <c r="J22" t="n">
         <v>45</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.538000106811523</v>
+        <v>6.375999927520752</v>
       </c>
       <c r="I23" t="n">
-        <v>1.529519705816713</v>
+        <v>1.568381448192457</v>
       </c>
       <c r="J23" t="n">
         <v>45</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>308.1000061035156</v>
+        <v>301.6000061035156</v>
       </c>
       <c r="I24" t="n">
-        <v>1.173320327291857</v>
+        <v>1.19860740279934</v>
       </c>
       <c r="J24" t="n">
         <v>45</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>27.10000038146973</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>5.018450113860267</v>
+        <v>5.112781881564981</v>
       </c>
       <c r="J25" t="n">
         <v>45</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.61999988555908</v>
+        <v>13.75</v>
       </c>
       <c r="I26" t="n">
-        <v>4.295154221111702</v>
+        <v>4.254545454545455</v>
       </c>
       <c r="J26" t="n">
         <v>45</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>16.06500053405762</v>
+        <v>15.72000026702881</v>
       </c>
       <c r="I27" t="n">
-        <v>3.921568497084126</v>
+        <v>4.00763351971033</v>
       </c>
       <c r="J27" t="n">
         <v>45</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>98.59999847412109</v>
+        <v>99.09999847412109</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9127789187909746</v>
+        <v>0.9081735760420071</v>
       </c>
       <c r="J28" t="n">
         <v>45</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>66.93000030517578</v>
+        <v>66.12000274658203</v>
       </c>
       <c r="I29" t="n">
-        <v>2.571044362996856</v>
+        <v>2.602540726737877</v>
       </c>
       <c r="J29" t="n">
         <v>45</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>25.10000038146973</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5577689158258186</v>
+        <v>0.5511811106401145</v>
       </c>
       <c r="J30" t="n">
         <v>38</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1.559999942779541</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I31" t="n">
-        <v>3.846153987229934</v>
+        <v>3.821655923277815</v>
       </c>
       <c r="J31" t="n">
         <v>38</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>20.21999931335449</v>
+        <v>20.52499961853027</v>
       </c>
       <c r="I32" t="n">
-        <v>1.285855632192235</v>
+        <v>1.266747891996393</v>
       </c>
       <c r="J32" t="n">
         <v>17</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>28.59499931335449</v>
+        <v>27.14500045776367</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3147403467779348</v>
+        <v>0.3315527665583786</v>
       </c>
       <c r="J33" t="n">
         <v>17</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>51.90000152587891</v>
+        <v>51.25</v>
       </c>
       <c r="I34" t="n">
-        <v>1.252408441020739</v>
+        <v>1.268292682926829</v>
       </c>
       <c r="J34" t="n">
         <v>-11</v>
@@ -2528,7 +2528,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2538,14 +2538,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2708,14 +2708,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2732,7 +2732,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2749,7 +2749,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2759,14 +2759,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2827,14 +2827,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2844,14 +2844,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2861,14 +2861,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2970,7 +2970,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2997,14 +2997,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3031,14 +3031,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3123,7 +3123,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3371,14 +3371,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3405,14 +3405,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3422,14 +3422,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3456,14 +3456,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3490,14 +3490,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3531,7 +3531,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3548,7 +3548,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3565,7 +3565,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3667,7 +3667,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3701,7 +3701,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3728,14 +3728,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3905,7 +3905,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3915,14 +3915,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3956,7 +3956,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4000,14 +4000,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4017,14 +4017,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4034,14 +4034,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4051,14 +4051,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4092,7 +4092,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4102,14 +4102,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4126,7 +4126,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4143,7 +4143,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4211,7 +4211,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4262,7 +4262,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4272,14 +4272,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4323,14 +4323,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4374,14 +4374,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4398,7 +4398,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4408,14 +4408,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4425,14 +4425,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4449,7 +4449,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4483,7 +4483,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4500,7 +4500,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4510,14 +4510,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4568,7 +4568,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4595,14 +4595,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4704,7 +4704,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4772,7 +4772,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4806,7 +4806,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4840,7 +4840,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4857,7 +4857,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4908,7 +4908,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4976,7 +4976,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5010,7 +5010,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5054,14 +5054,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5112,7 +5112,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5139,14 +5139,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5156,14 +5156,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5180,7 +5180,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5197,7 +5197,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5214,7 +5214,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5248,7 +5248,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5275,14 +5275,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5299,7 +5299,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5350,7 +5350,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5367,7 +5367,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5384,7 +5384,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5418,7 +5418,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5445,14 +5445,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5469,7 +5469,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5496,14 +5496,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5520,7 +5520,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5530,14 +5530,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5554,7 +5554,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5588,7 +5588,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5598,14 +5598,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5622,7 +5622,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5632,14 +5632,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5649,14 +5649,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5673,7 +5673,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5683,14 +5683,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5707,7 +5707,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5741,7 +5741,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5775,7 +5775,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5802,14 +5802,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5819,14 +5819,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5843,7 +5843,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5877,7 +5877,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5887,14 +5887,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5911,7 +5911,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5928,7 +5928,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5945,7 +5945,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5962,7 +5962,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5979,7 +5979,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6013,7 +6013,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6040,14 +6040,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6064,7 +6064,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6081,7 +6081,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6091,14 +6091,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6125,14 +6125,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6142,14 +6142,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6200,7 +6200,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6234,7 +6234,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6251,7 +6251,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6261,14 +6261,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6336,7 +6336,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6346,14 +6346,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6363,14 +6363,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6387,7 +6387,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6404,7 +6404,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6421,7 +6421,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6438,7 +6438,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6472,7 +6472,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6482,14 +6482,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6506,7 +6506,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6523,7 +6523,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6540,7 +6540,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6557,7 +6557,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6574,7 +6574,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6591,7 +6591,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6625,7 +6625,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6642,7 +6642,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6659,7 +6659,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6676,7 +6676,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6693,7 +6693,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6727,7 +6727,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6744,7 +6744,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6778,7 +6778,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6795,7 +6795,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6812,7 +6812,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6829,7 +6829,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6846,7 +6846,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6863,7 +6863,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6880,7 +6880,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6897,7 +6897,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6907,14 +6907,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6999,7 +6999,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7016,7 +7016,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7033,7 +7033,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7050,7 +7050,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7084,7 +7084,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7118,7 +7118,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7135,7 +7135,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7152,7 +7152,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7169,7 +7169,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7186,7 +7186,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7203,7 +7203,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7237,7 +7237,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7254,7 +7254,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7271,7 +7271,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7288,7 +7288,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7305,7 +7305,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7315,14 +7315,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7339,7 +7339,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7349,14 +7349,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7373,7 +7373,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7390,7 +7390,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7407,7 +7407,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7441,7 +7441,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7458,7 +7458,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7475,7 +7475,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7485,14 +7485,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7509,7 +7509,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7543,7 +7543,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7553,14 +7553,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7577,7 +7577,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7594,7 +7594,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7655,14 +7655,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7774,14 +7774,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -7927,14 +7927,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8080,14 +8080,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8182,14 +8182,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8199,14 +8199,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8216,14 +8216,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8250,14 +8250,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8301,14 +8301,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8352,14 +8352,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -8386,14 +8386,14 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8486,314 +8486,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004056880</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10.52000045776367</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2.756653872443346</v>
-      </c>
-      <c r="I2" t="n">
-        <v>73</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0003261697</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>33.61999893188477</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5.948840165200679</v>
-      </c>
-      <c r="I3" t="n">
-        <v>73</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NL0015435975</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-04-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6.538000106811523</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.529519705816713</v>
-      </c>
-      <c r="I4" t="n">
-        <v>45</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0005455875</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>12.30000019073486</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.197169</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1.60299997514244</v>
-      </c>
-      <c r="I5" t="n">
-        <v>59</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nexi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005366767</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2.822000026702881</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>10.63075822683492</v>
-      </c>
-      <c r="I6" t="n">
-        <v>73</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0003153415</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6.464000225067139</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1813</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2.804764753827293</v>
-      </c>
-      <c r="I7" t="n">
-        <v>108</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8804,61 +8499,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Avio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>